--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.727307961972449</v>
+        <v>0.4431875438205229</v>
       </c>
       <c r="D2" t="n">
-        <v>3.081700552665461</v>
+        <v>0.5007763398081374</v>
       </c>
       <c r="E2" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F2" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.72004514666935</v>
+        <v>2.87950733633377</v>
       </c>
       <c r="D3" t="n">
-        <v>17.31924888676864</v>
+        <v>2.814377944099904</v>
       </c>
       <c r="E3" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F3" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57061941771634</v>
+        <v>8.867725655378907</v>
       </c>
       <c r="D4" t="n">
-        <v>55.3298535077389</v>
+        <v>8.991101195007571</v>
       </c>
       <c r="E4" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F4" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="D5" t="n">
-        <v>5.781529120529762</v>
+        <v>0.9394984820860863</v>
       </c>
       <c r="E5" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F5" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.02629759044045</v>
+        <v>3.091773358446573</v>
       </c>
       <c r="D6" t="n">
-        <v>19.83917199981392</v>
+        <v>3.223865449969762</v>
       </c>
       <c r="E6" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F6" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.199901885687699</v>
+        <v>0.6824840564242511</v>
       </c>
       <c r="D7" t="n">
-        <v>4.685598405226338</v>
+        <v>0.7614097408492799</v>
       </c>
       <c r="E7" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F7" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.23813663153998</v>
+        <v>5.563697202625247</v>
       </c>
       <c r="D8" t="n">
-        <v>33.6340874195702</v>
+        <v>5.465539205680158</v>
       </c>
       <c r="E8" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F8" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.37821358770326</v>
+        <v>3.473959708001781</v>
       </c>
       <c r="D9" t="n">
-        <v>22.96655983638142</v>
+        <v>3.73206597341198</v>
       </c>
       <c r="E9" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F9" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.35065917948039</v>
+        <v>3.794482116665564</v>
       </c>
       <c r="D10" t="n">
-        <v>24.08000995123912</v>
+        <v>3.913001617076358</v>
       </c>
       <c r="E10" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F10" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.22294624543134</v>
+        <v>2.473728764882592</v>
       </c>
       <c r="D11" t="n">
-        <v>13.71415308116414</v>
+        <v>2.228549875689172</v>
       </c>
       <c r="E11" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F11" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.76378421731118</v>
+        <v>3.211614935313066</v>
       </c>
       <c r="D12" t="n">
-        <v>18.43739617575977</v>
+        <v>2.996076878560963</v>
       </c>
       <c r="E12" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F12" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.88748179237413</v>
+        <v>6.319215791260796</v>
       </c>
       <c r="D13" t="n">
-        <v>37.52814536128454</v>
+        <v>6.098323621208737</v>
       </c>
       <c r="E13" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F13" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.65922010601988</v>
+        <v>7.094623267228231</v>
       </c>
       <c r="D14" t="n">
-        <v>44.18599730544567</v>
+        <v>7.180224562134921</v>
       </c>
       <c r="E14" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F14" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.99773220037601</v>
+        <v>8.124631482561101</v>
       </c>
       <c r="D15" t="n">
-        <v>50.77998472897854</v>
+        <v>8.251747518459013</v>
       </c>
       <c r="E15" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F15" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.70393949843572</v>
+        <v>9.376890168495803</v>
       </c>
       <c r="D16" t="n">
-        <v>58.42836977629327</v>
+        <v>9.494610088647658</v>
       </c>
       <c r="E16" t="n">
-        <v>17.60810600875793</v>
+        <v>2.861317226423164</v>
       </c>
       <c r="F16" t="n">
-        <v>17.78455091957526</v>
+        <v>2.88998952443098</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
